--- a/BOM_Biosci Uc.xlsx
+++ b/BOM_Biosci Uc.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4937E700-7A2B-4EDA-B868-731E5656304F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BA9436D-800D-409E-AE65-A0D88D3B8D24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="244" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="2" r:id="rId1"/>
@@ -1974,22 +1974,22 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J165"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.21875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="11.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.5546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="17.5546875" style="2" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="94.77734375" style="3" customWidth="1"/>
-    <col min="6" max="6" width="8.21875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="8.44140625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="31.5546875" style="35" customWidth="1"/>
-    <col min="9" max="9" width="30.21875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="10.77734375" style="2" customWidth="1"/>
-    <col min="11" max="16384" width="9.21875" style="1"/>
+    <col min="1" max="1" width="10.28515625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.5703125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="17.5703125" style="2" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="94.7109375" style="3" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="8.42578125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="31.5703125" style="35" customWidth="1"/>
+    <col min="9" max="9" width="30.28515625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="9.28515625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="81" t="s">
         <v>244</v>
       </c>
@@ -2002,7 +2002,7 @@
       <c r="H1" s="39"/>
       <c r="I1" s="39"/>
     </row>
-    <row r="2" spans="1:10" s="3" customFormat="1" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" s="3" customFormat="1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
         <v>0</v>
       </c>
@@ -2034,7 +2034,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
         <v>8</v>
       </c>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="J3" s="12"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
       <c r="B4" s="4"/>
       <c r="C4" s="6"/>
@@ -2062,7 +2062,7 @@
       <c r="I4" s="9"/>
       <c r="J4" s="5"/>
     </row>
-    <row r="5" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A5" s="18" t="s">
         <v>9</v>
       </c>
@@ -2076,7 +2076,7 @@
       <c r="I5" s="11"/>
       <c r="J5" s="12"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
       <c r="B6" s="5"/>
       <c r="C6" s="9"/>
@@ -2088,7 +2088,7 @@
       <c r="I6" s="9"/>
       <c r="J6" s="5"/>
     </row>
-    <row r="7" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A7" s="18" t="s">
         <v>10</v>
       </c>
@@ -2102,7 +2102,7 @@
       <c r="I7" s="11"/>
       <c r="J7" s="12"/>
     </row>
-    <row r="8" spans="1:10" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>1</v>
       </c>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="J8" s="5"/>
     </row>
-    <row r="9" spans="1:10" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>2</v>
       </c>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="J9" s="5"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>5</v>
       </c>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="J10" s="5"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>8</v>
       </c>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="J11" s="5"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>9</v>
       </c>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="J12" s="5"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>10</v>
       </c>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="J13" s="5"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -2270,7 +2270,7 @@
       <c r="I14" s="9"/>
       <c r="J14" s="5"/>
     </row>
-    <row r="15" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
         <v>17</v>
       </c>
@@ -2284,7 +2284,7 @@
       <c r="I15" s="11"/>
       <c r="J15" s="12"/>
     </row>
-    <row r="16" spans="1:10" s="10" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
       <c r="B16" s="15"/>
       <c r="C16" s="73" t="s">
@@ -2302,7 +2302,7 @@
       <c r="I16" s="11"/>
       <c r="J16" s="12"/>
     </row>
-    <row r="17" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A17" s="5">
         <v>1</v>
       </c>
@@ -2334,7 +2334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A18" s="5">
         <v>2</v>
       </c>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="J18" s="12"/>
     </row>
-    <row r="19" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A19" s="5">
         <v>3</v>
       </c>
@@ -2396,7 +2396,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <v>4</v>
       </c>
@@ -2428,7 +2428,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>5</v>
       </c>
@@ -2456,7 +2456,7 @@
       </c>
       <c r="J21" s="12"/>
     </row>
-    <row r="22" spans="1:10" s="10" customFormat="1" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" s="10" customFormat="1" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>6</v>
       </c>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="J22" s="12"/>
     </row>
-    <row r="23" spans="1:10" s="10" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" s="10" customFormat="1" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>7</v>
       </c>
@@ -2514,7 +2514,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A24" s="18"/>
       <c r="B24" s="18"/>
       <c r="C24" s="18"/>
@@ -2526,7 +2526,7 @@
       <c r="I24" s="11"/>
       <c r="J24" s="12"/>
     </row>
-    <row r="25" spans="1:10" s="10" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="69"/>
       <c r="B25" s="15"/>
       <c r="C25" s="73" t="s">
@@ -2546,7 +2546,7 @@
       <c r="I25" s="11"/>
       <c r="J25" s="12"/>
     </row>
-    <row r="26" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A26" s="69">
         <v>1</v>
       </c>
@@ -2574,7 +2574,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A27" s="69">
         <v>2</v>
       </c>
@@ -2602,7 +2602,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="28" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A28" s="69">
         <v>3</v>
       </c>
@@ -2630,7 +2630,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A29" s="69">
         <v>4</v>
       </c>
@@ -2660,7 +2660,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:10" s="16" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" s="16" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="69">
         <v>5</v>
       </c>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="J30" s="12"/>
     </row>
-    <row r="31" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A31" s="23">
         <v>6</v>
       </c>
@@ -2714,7 +2714,7 @@
       <c r="I31" s="11"/>
       <c r="J31" s="12"/>
     </row>
-    <row r="32" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A32" s="23">
         <v>7</v>
       </c>
@@ -2738,7 +2738,7 @@
       <c r="I32" s="11"/>
       <c r="J32" s="12"/>
     </row>
-    <row r="33" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A33" s="23"/>
       <c r="B33" s="18"/>
       <c r="C33" s="66"/>
@@ -2750,7 +2750,7 @@
       <c r="I33" s="11"/>
       <c r="J33" s="12"/>
     </row>
-    <row r="34" spans="1:10" s="10" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="18"/>
       <c r="B34" s="15"/>
       <c r="C34" s="73" t="s">
@@ -2768,7 +2768,7 @@
       <c r="I34" s="11"/>
       <c r="J34" s="12"/>
     </row>
-    <row r="35" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A35" s="69">
         <v>1</v>
       </c>
@@ -2800,7 +2800,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="36" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A36" s="69">
         <v>2</v>
       </c>
@@ -2832,7 +2832,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A37" s="69">
         <v>3</v>
       </c>
@@ -2864,7 +2864,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A38" s="69">
         <v>4</v>
       </c>
@@ -2892,7 +2892,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A39" s="69">
         <v>5</v>
       </c>
@@ -2922,7 +2922,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:10" s="16" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" s="16" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="69">
         <v>6</v>
       </c>
@@ -2954,7 +2954,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="41" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" s="10" customFormat="1" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A41" s="69">
         <v>7</v>
       </c>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="J41" s="12"/>
     </row>
-    <row r="42" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A42" s="69">
         <v>8</v>
       </c>
@@ -3014,7 +3014,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A43" s="69">
         <v>9</v>
       </c>
@@ -3040,7 +3040,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="44" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A44" s="69">
         <v>10</v>
       </c>
@@ -3066,7 +3066,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A45" s="69">
         <v>11</v>
       </c>
@@ -3092,7 +3092,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A46" s="18"/>
       <c r="B46" s="18"/>
       <c r="C46" s="18"/>
@@ -3104,7 +3104,7 @@
       <c r="I46" s="11"/>
       <c r="J46" s="12"/>
     </row>
-    <row r="47" spans="1:10" s="16" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A47" s="18" t="s">
         <v>21</v>
       </c>
@@ -3118,7 +3118,7 @@
       <c r="I47" s="17"/>
       <c r="J47" s="15"/>
     </row>
-    <row r="48" spans="1:10" s="16" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" s="16" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="15">
         <v>1</v>
       </c>
@@ -3148,7 +3148,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="49" spans="1:10" s="16" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" s="16" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="15"/>
       <c r="B49" s="76" t="s">
         <v>283</v>
@@ -3172,7 +3172,7 @@
       <c r="I49" s="46"/>
       <c r="J49" s="15"/>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="5"/>
       <c r="B50" s="5" t="s">
         <v>53</v>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="J50" s="5"/>
     </row>
-    <row r="51" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="15"/>
       <c r="B51" s="31" t="s">
         <v>55</v>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="J51" s="5"/>
     </row>
-    <row r="52" spans="1:10" s="16" customFormat="1" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" s="16" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5"/>
       <c r="B52" s="31" t="s">
         <v>57</v>
@@ -3250,7 +3250,7 @@
       </c>
       <c r="J52" s="15"/>
     </row>
-    <row r="53" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="15"/>
       <c r="B53" s="5" t="s">
         <v>58</v>
@@ -3278,7 +3278,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5"/>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
@@ -3290,7 +3290,7 @@
       <c r="I54" s="11"/>
       <c r="J54" s="5"/>
     </row>
-    <row r="55" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A55" s="18" t="s">
         <v>25</v>
       </c>
@@ -3303,7 +3303,7 @@
       <c r="I55" s="11"/>
       <c r="J55" s="12"/>
     </row>
-    <row r="56" spans="1:10" s="16" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A56" s="15"/>
       <c r="B56" s="15"/>
       <c r="C56" s="15"/>
@@ -3315,7 +3315,7 @@
       <c r="I56" s="48"/>
       <c r="J56" s="15"/>
     </row>
-    <row r="57" spans="1:10" s="16" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A57" s="18" t="s">
         <v>26</v>
       </c>
@@ -3331,7 +3331,7 @@
       <c r="I57" s="17"/>
       <c r="J57" s="15"/>
     </row>
-    <row r="58" spans="1:10" s="16" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A58" s="18"/>
       <c r="B58" s="18"/>
       <c r="C58" s="18"/>
@@ -3343,7 +3343,7 @@
       <c r="I58" s="63"/>
       <c r="J58" s="15"/>
     </row>
-    <row r="59" spans="1:10" s="16" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A59" s="18" t="s">
         <v>28</v>
       </c>
@@ -3357,7 +3357,7 @@
       <c r="I59" s="17"/>
       <c r="J59" s="15"/>
     </row>
-    <row r="60" spans="1:10" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A60" s="15">
         <v>1</v>
       </c>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="J60" s="15"/>
     </row>
-    <row r="61" spans="1:10" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A61" s="15">
         <v>2</v>
       </c>
@@ -3409,7 +3409,7 @@
       </c>
       <c r="J61" s="15"/>
     </row>
-    <row r="62" spans="1:10" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A62" s="15">
         <v>3</v>
       </c>
@@ -3435,7 +3435,7 @@
       </c>
       <c r="J62" s="15"/>
     </row>
-    <row r="63" spans="1:10" s="16" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A63" s="18" t="s">
         <v>31</v>
       </c>
@@ -3449,7 +3449,7 @@
       <c r="I63" s="17"/>
       <c r="J63" s="15"/>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="5">
         <v>1</v>
       </c>
@@ -3471,7 +3471,7 @@
       <c r="I64" s="9"/>
       <c r="J64" s="5"/>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="5">
         <v>2</v>
       </c>
@@ -3493,7 +3493,7 @@
       <c r="I65" s="9"/>
       <c r="J65" s="5"/>
     </row>
-    <row r="66" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="5">
         <v>3</v>
       </c>
@@ -3515,7 +3515,7 @@
       <c r="I66" s="9"/>
       <c r="J66" s="5"/>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="5">
         <v>4</v>
       </c>
@@ -3537,7 +3537,7 @@
       <c r="I67" s="9"/>
       <c r="J67" s="5"/>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A68" s="5">
         <v>6</v>
       </c>
@@ -3557,7 +3557,7 @@
       <c r="I68" s="9"/>
       <c r="J68" s="5"/>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="5">
         <v>7</v>
       </c>
@@ -3579,7 +3579,7 @@
       <c r="I69" s="9"/>
       <c r="J69" s="5"/>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="5">
         <v>8</v>
       </c>
@@ -3601,7 +3601,7 @@
       <c r="I70" s="9"/>
       <c r="J70" s="5"/>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="5">
         <v>9</v>
       </c>
@@ -3623,7 +3623,7 @@
       <c r="I71" s="9"/>
       <c r="J71" s="5"/>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="5">
         <v>10</v>
       </c>
@@ -3645,7 +3645,7 @@
       <c r="I72" s="9"/>
       <c r="J72" s="5"/>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="5">
         <v>11</v>
       </c>
@@ -3667,7 +3667,7 @@
       <c r="I73" s="9"/>
       <c r="J73" s="5"/>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="5">
         <v>12</v>
       </c>
@@ -3689,7 +3689,7 @@
       <c r="I74" s="9"/>
       <c r="J74" s="5"/>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="5">
         <v>13</v>
       </c>
@@ -3711,7 +3711,7 @@
       <c r="I75" s="9"/>
       <c r="J75" s="5"/>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="5">
         <v>14</v>
       </c>
@@ -3733,7 +3733,7 @@
       <c r="I76" s="9"/>
       <c r="J76" s="5"/>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="5">
         <v>15</v>
       </c>
@@ -3755,7 +3755,7 @@
       <c r="I77" s="9"/>
       <c r="J77" s="5"/>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="5">
         <v>16</v>
       </c>
@@ -3777,7 +3777,7 @@
       <c r="I78" s="9"/>
       <c r="J78" s="5"/>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="5">
         <v>17</v>
       </c>
@@ -3799,7 +3799,7 @@
       <c r="I79" s="9"/>
       <c r="J79" s="5"/>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="5">
         <v>18</v>
       </c>
@@ -3821,7 +3821,7 @@
       <c r="I80" s="9"/>
       <c r="J80" s="5"/>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="5">
         <v>19</v>
       </c>
@@ -3841,7 +3841,7 @@
       <c r="I81" s="9"/>
       <c r="J81" s="5"/>
     </row>
-    <row r="84" spans="1:10" s="21" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:10" s="21" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" s="79" t="s">
         <v>59</v>
       </c>
@@ -3856,7 +3856,7 @@
       <c r="H84" s="37"/>
       <c r="J84" s="20"/>
     </row>
-    <row r="87" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -3865,7 +3865,7 @@
       <c r="H87" s="35"/>
       <c r="I87" s="1"/>
     </row>
-    <row r="88" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -3874,7 +3874,7 @@
       <c r="H88" s="35"/>
       <c r="I88" s="1"/>
     </row>
-    <row r="89" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -3883,7 +3883,7 @@
       <c r="H89" s="35"/>
       <c r="I89" s="1"/>
     </row>
-    <row r="90" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -3892,7 +3892,7 @@
       <c r="H90" s="35"/>
       <c r="I90" s="1"/>
     </row>
-    <row r="91" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -3901,7 +3901,7 @@
       <c r="H91" s="35"/>
       <c r="I91" s="1"/>
     </row>
-    <row r="92" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -3910,7 +3910,7 @@
       <c r="H92" s="35"/>
       <c r="I92" s="1"/>
     </row>
-    <row r="93" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -3919,7 +3919,7 @@
       <c r="H93" s="35"/>
       <c r="I93" s="1"/>
     </row>
-    <row r="94" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -3928,7 +3928,7 @@
       <c r="H94" s="35"/>
       <c r="I94" s="1"/>
     </row>
-    <row r="95" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -3937,7 +3937,7 @@
       <c r="H95" s="35"/>
       <c r="I95" s="1"/>
     </row>
-    <row r="96" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -3946,7 +3946,7 @@
       <c r="H96" s="35"/>
       <c r="I96" s="1"/>
     </row>
-    <row r="97" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -3955,7 +3955,7 @@
       <c r="H97" s="35"/>
       <c r="I97" s="1"/>
     </row>
-    <row r="98" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -3964,7 +3964,7 @@
       <c r="H98" s="35"/>
       <c r="I98" s="1"/>
     </row>
-    <row r="99" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -3973,7 +3973,7 @@
       <c r="H99" s="35"/>
       <c r="I99" s="1"/>
     </row>
-    <row r="100" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -3982,7 +3982,7 @@
       <c r="H100" s="35"/>
       <c r="I100" s="1"/>
     </row>
-    <row r="101" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -3991,7 +3991,7 @@
       <c r="H101" s="35"/>
       <c r="I101" s="1"/>
     </row>
-    <row r="102" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -4000,7 +4000,7 @@
       <c r="H102" s="35"/>
       <c r="I102" s="1"/>
     </row>
-    <row r="103" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -4009,7 +4009,7 @@
       <c r="H103" s="35"/>
       <c r="I103" s="1"/>
     </row>
-    <row r="104" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -4018,7 +4018,7 @@
       <c r="H104" s="35"/>
       <c r="I104" s="1"/>
     </row>
-    <row r="105" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -4027,7 +4027,7 @@
       <c r="H105" s="35"/>
       <c r="I105" s="1"/>
     </row>
-    <row r="106" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -4036,7 +4036,7 @@
       <c r="H106" s="35"/>
       <c r="I106" s="1"/>
     </row>
-    <row r="107" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -4045,7 +4045,7 @@
       <c r="H107" s="35"/>
       <c r="I107" s="1"/>
     </row>
-    <row r="108" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -4054,7 +4054,7 @@
       <c r="H108" s="35"/>
       <c r="I108" s="1"/>
     </row>
-    <row r="109" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -4063,7 +4063,7 @@
       <c r="H109" s="35"/>
       <c r="I109" s="1"/>
     </row>
-    <row r="110" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -4072,7 +4072,7 @@
       <c r="H110" s="35"/>
       <c r="I110" s="1"/>
     </row>
-    <row r="111" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -4081,7 +4081,7 @@
       <c r="H111" s="35"/>
       <c r="I111" s="1"/>
     </row>
-    <row r="112" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -4090,7 +4090,7 @@
       <c r="H112" s="35"/>
       <c r="I112" s="1"/>
     </row>
-    <row r="113" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -4099,7 +4099,7 @@
       <c r="H113" s="35"/>
       <c r="I113" s="1"/>
     </row>
-    <row r="114" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -4108,7 +4108,7 @@
       <c r="H114" s="35"/>
       <c r="I114" s="1"/>
     </row>
-    <row r="115" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -4117,7 +4117,7 @@
       <c r="H115" s="35"/>
       <c r="I115" s="1"/>
     </row>
-    <row r="116" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -4126,7 +4126,7 @@
       <c r="H116" s="35"/>
       <c r="I116" s="1"/>
     </row>
-    <row r="117" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -4135,7 +4135,7 @@
       <c r="H117" s="35"/>
       <c r="I117" s="1"/>
     </row>
-    <row r="118" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -4144,7 +4144,7 @@
       <c r="H118" s="35"/>
       <c r="I118" s="1"/>
     </row>
-    <row r="119" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -4153,7 +4153,7 @@
       <c r="H119" s="35"/>
       <c r="I119" s="1"/>
     </row>
-    <row r="120" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -4162,7 +4162,7 @@
       <c r="H120" s="35"/>
       <c r="I120" s="1"/>
     </row>
-    <row r="121" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -4171,7 +4171,7 @@
       <c r="H121" s="35"/>
       <c r="I121" s="1"/>
     </row>
-    <row r="122" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -4180,7 +4180,7 @@
       <c r="H122" s="35"/>
       <c r="I122" s="1"/>
     </row>
-    <row r="123" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -4189,7 +4189,7 @@
       <c r="H123" s="35"/>
       <c r="I123" s="1"/>
     </row>
-    <row r="124" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -4198,7 +4198,7 @@
       <c r="H124" s="35"/>
       <c r="I124" s="1"/>
     </row>
-    <row r="125" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -4207,7 +4207,7 @@
       <c r="H125" s="35"/>
       <c r="I125" s="1"/>
     </row>
-    <row r="126" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -4216,7 +4216,7 @@
       <c r="H126" s="35"/>
       <c r="I126" s="1"/>
     </row>
-    <row r="127" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -4225,7 +4225,7 @@
       <c r="H127" s="35"/>
       <c r="I127" s="1"/>
     </row>
-    <row r="128" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -4234,7 +4234,7 @@
       <c r="H128" s="35"/>
       <c r="I128" s="1"/>
     </row>
-    <row r="129" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -4243,7 +4243,7 @@
       <c r="H129" s="35"/>
       <c r="I129" s="1"/>
     </row>
-    <row r="130" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -4252,7 +4252,7 @@
       <c r="H130" s="35"/>
       <c r="I130" s="1"/>
     </row>
-    <row r="131" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -4261,7 +4261,7 @@
       <c r="H131" s="35"/>
       <c r="I131" s="1"/>
     </row>
-    <row r="132" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -4270,7 +4270,7 @@
       <c r="H132" s="35"/>
       <c r="I132" s="1"/>
     </row>
-    <row r="133" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -4279,7 +4279,7 @@
       <c r="H133" s="35"/>
       <c r="I133" s="1"/>
     </row>
-    <row r="134" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -4288,7 +4288,7 @@
       <c r="H134" s="35"/>
       <c r="I134" s="1"/>
     </row>
-    <row r="135" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -4297,7 +4297,7 @@
       <c r="H135" s="35"/>
       <c r="I135" s="1"/>
     </row>
-    <row r="136" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -4306,7 +4306,7 @@
       <c r="H136" s="35"/>
       <c r="I136" s="1"/>
     </row>
-    <row r="137" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -4315,7 +4315,7 @@
       <c r="H137" s="35"/>
       <c r="I137" s="1"/>
     </row>
-    <row r="138" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -4324,7 +4324,7 @@
       <c r="H138" s="35"/>
       <c r="I138" s="1"/>
     </row>
-    <row r="139" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -4333,7 +4333,7 @@
       <c r="H139" s="35"/>
       <c r="I139" s="1"/>
     </row>
-    <row r="140" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -4342,7 +4342,7 @@
       <c r="H140" s="35"/>
       <c r="I140" s="1"/>
     </row>
-    <row r="141" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -4351,7 +4351,7 @@
       <c r="H141" s="35"/>
       <c r="I141" s="1"/>
     </row>
-    <row r="142" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -4360,7 +4360,7 @@
       <c r="H142" s="35"/>
       <c r="I142" s="1"/>
     </row>
-    <row r="143" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -4369,7 +4369,7 @@
       <c r="H143" s="35"/>
       <c r="I143" s="1"/>
     </row>
-    <row r="144" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -4378,7 +4378,7 @@
       <c r="H144" s="35"/>
       <c r="I144" s="1"/>
     </row>
-    <row r="145" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -4387,7 +4387,7 @@
       <c r="H145" s="35"/>
       <c r="I145" s="1"/>
     </row>
-    <row r="146" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -4396,7 +4396,7 @@
       <c r="H146" s="35"/>
       <c r="I146" s="1"/>
     </row>
-    <row r="147" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -4405,7 +4405,7 @@
       <c r="H147" s="35"/>
       <c r="I147" s="1"/>
     </row>
-    <row r="148" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -4414,7 +4414,7 @@
       <c r="H148" s="35"/>
       <c r="I148" s="1"/>
     </row>
-    <row r="149" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -4423,7 +4423,7 @@
       <c r="H149" s="35"/>
       <c r="I149" s="1"/>
     </row>
-    <row r="150" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -4432,7 +4432,7 @@
       <c r="H150" s="35"/>
       <c r="I150" s="1"/>
     </row>
-    <row r="151" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -4441,7 +4441,7 @@
       <c r="H151" s="35"/>
       <c r="I151" s="1"/>
     </row>
-    <row r="152" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -4450,7 +4450,7 @@
       <c r="H152" s="35"/>
       <c r="I152" s="1"/>
     </row>
-    <row r="153" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -4459,7 +4459,7 @@
       <c r="H153" s="35"/>
       <c r="I153" s="1"/>
     </row>
-    <row r="154" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -4468,7 +4468,7 @@
       <c r="H154" s="35"/>
       <c r="I154" s="1"/>
     </row>
-    <row r="155" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -4477,7 +4477,7 @@
       <c r="H155" s="35"/>
       <c r="I155" s="1"/>
     </row>
-    <row r="156" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -4486,7 +4486,7 @@
       <c r="H156" s="35"/>
       <c r="I156" s="1"/>
     </row>
-    <row r="157" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -4495,7 +4495,7 @@
       <c r="H157" s="35"/>
       <c r="I157" s="1"/>
     </row>
-    <row r="158" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -4504,7 +4504,7 @@
       <c r="H158" s="35"/>
       <c r="I158" s="1"/>
     </row>
-    <row r="159" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -4513,7 +4513,7 @@
       <c r="H159" s="35"/>
       <c r="I159" s="1"/>
     </row>
-    <row r="160" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -4522,7 +4522,7 @@
       <c r="H160" s="35"/>
       <c r="I160" s="1"/>
     </row>
-    <row r="161" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -4531,7 +4531,7 @@
       <c r="H161" s="35"/>
       <c r="I161" s="1"/>
     </row>
-    <row r="162" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -4540,7 +4540,7 @@
       <c r="H162" s="35"/>
       <c r="I162" s="1"/>
     </row>
-    <row r="163" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -4549,7 +4549,7 @@
       <c r="H163" s="35"/>
       <c r="I163" s="1"/>
     </row>
-    <row r="164" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -4558,7 +4558,7 @@
       <c r="H164" s="35"/>
       <c r="I164" s="1"/>
     </row>
-    <row r="165" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -4597,15 +4597,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC3B58F3-4F81-4374-839A-DA060915BB5F}">
   <dimension ref="A1:C55"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" customWidth="1"/>
-    <col min="2" max="2" width="34.33203125" style="58" customWidth="1"/>
-    <col min="3" max="3" width="49.33203125" style="58" customWidth="1"/>
+    <col min="1" max="1" width="9.28515625" customWidth="1"/>
+    <col min="2" max="2" width="34.28515625" style="58" customWidth="1"/>
+    <col min="3" max="3" width="49.28515625" style="58" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="1:3" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:3" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="50" t="s">
         <v>186</v>
       </c>
@@ -4616,7 +4616,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="51" x14ac:dyDescent="0.25">
       <c r="A3" s="53">
         <v>1</v>
       </c>
@@ -4627,7 +4627,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A4" s="53">
         <v>2</v>
       </c>
@@ -4638,7 +4638,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="51" x14ac:dyDescent="0.25">
       <c r="A5" s="53">
         <v>3</v>
       </c>
@@ -4649,7 +4649,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="51" x14ac:dyDescent="0.25">
       <c r="A6" s="53">
         <v>4</v>
       </c>
@@ -4660,7 +4660,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A7" s="53">
         <v>5</v>
       </c>
@@ -4671,7 +4671,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A8" s="53">
         <v>6</v>
       </c>
@@ -4682,7 +4682,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A9" s="53">
         <v>7</v>
       </c>
@@ -4693,7 +4693,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="51" x14ac:dyDescent="0.25">
       <c r="A10" s="53">
         <v>8</v>
       </c>
@@ -4704,7 +4704,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" ht="51" x14ac:dyDescent="0.25">
       <c r="A11" s="53">
         <v>9</v>
       </c>
@@ -4715,7 +4715,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" ht="51" x14ac:dyDescent="0.25">
       <c r="A12" s="53">
         <v>10</v>
       </c>
@@ -4726,7 +4726,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A13" s="53">
         <v>11</v>
       </c>
@@ -4737,7 +4737,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="69" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A14" s="53">
         <v>12</v>
       </c>
@@ -4748,7 +4748,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A15" s="53">
         <v>13</v>
       </c>
@@ -4759,7 +4759,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="82.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A16" s="53">
         <v>14</v>
       </c>
@@ -4770,7 +4770,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="69" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A17" s="53">
         <v>15</v>
       </c>
@@ -4781,7 +4781,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" ht="51" x14ac:dyDescent="0.25">
       <c r="A18" s="53">
         <v>16</v>
       </c>
@@ -4792,7 +4792,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" ht="51" x14ac:dyDescent="0.25">
       <c r="A19" s="53">
         <v>17</v>
       </c>
@@ -4803,7 +4803,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="53">
         <v>18</v>
       </c>
@@ -4812,7 +4812,7 @@
       </c>
       <c r="C20" s="56"/>
     </row>
-    <row r="21" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" ht="51" x14ac:dyDescent="0.25">
       <c r="A21" s="53">
         <v>19</v>
       </c>
@@ -4823,7 +4823,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A22" s="53">
         <v>20</v>
       </c>
@@ -4834,7 +4834,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" ht="51" x14ac:dyDescent="0.25">
       <c r="A23" s="53">
         <v>21</v>
       </c>
@@ -4845,7 +4845,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" ht="51" x14ac:dyDescent="0.25">
       <c r="A24" s="53">
         <v>22</v>
       </c>
@@ -4854,7 +4854,7 @@
       </c>
       <c r="C24" s="56"/>
     </row>
-    <row r="25" spans="1:3" ht="82.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A25" s="54">
         <v>23</v>
       </c>
@@ -4865,7 +4865,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A26" s="53">
         <v>24</v>
       </c>
@@ -4876,7 +4876,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" ht="51" x14ac:dyDescent="0.25">
       <c r="A27" s="53">
         <v>25</v>
       </c>
@@ -4887,7 +4887,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="82.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A28" s="53">
         <v>26</v>
       </c>
@@ -4898,7 +4898,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A29" s="53">
         <v>27</v>
       </c>
@@ -4909,7 +4909,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A30" s="53">
         <v>28</v>
       </c>
@@ -4920,7 +4920,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A31" s="53">
         <v>29</v>
       </c>
@@ -4931,7 +4931,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" ht="51" x14ac:dyDescent="0.25">
       <c r="A32" s="53">
         <v>30</v>
       </c>
@@ -4942,7 +4942,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A33" s="53">
         <v>31</v>
       </c>
@@ -4953,7 +4953,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A34" s="53">
         <v>32</v>
       </c>
@@ -4964,7 +4964,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A35" s="53">
         <v>33</v>
       </c>
@@ -4975,7 +4975,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A36" s="53">
         <v>34</v>
       </c>
@@ -4986,7 +4986,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A37" s="53">
         <v>35</v>
       </c>
@@ -4997,7 +4997,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" ht="51" x14ac:dyDescent="0.25">
       <c r="A38" s="53">
         <v>36</v>
       </c>
@@ -5008,7 +5008,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A39" s="53">
         <v>37</v>
       </c>
@@ -5019,7 +5019,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A40" s="53">
         <v>38</v>
       </c>
@@ -5030,7 +5030,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" ht="51" x14ac:dyDescent="0.25">
       <c r="A41" s="53">
         <v>39</v>
       </c>
@@ -5041,7 +5041,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="69" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A42" s="53">
         <v>40</v>
       </c>
@@ -5052,7 +5052,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A43" s="53">
         <v>41</v>
       </c>
@@ -5063,7 +5063,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A44" s="53">
         <v>42</v>
       </c>
@@ -5074,7 +5074,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A45" s="53">
         <v>43</v>
       </c>
@@ -5085,7 +5085,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A46" s="53">
         <v>44</v>
       </c>
@@ -5096,7 +5096,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A47" s="53">
         <v>45</v>
       </c>
@@ -5107,7 +5107,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A48" s="53">
         <v>46</v>
       </c>
@@ -5118,7 +5118,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A49" s="53">
         <v>47</v>
       </c>
@@ -5129,7 +5129,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" ht="51" x14ac:dyDescent="0.25">
       <c r="A50" s="53">
         <v>48</v>
       </c>
@@ -5140,7 +5140,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A51" s="53">
         <v>49</v>
       </c>
@@ -5151,7 +5151,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" ht="90" x14ac:dyDescent="0.25">
       <c r="A52" s="53">
         <v>50</v>
       </c>
@@ -5162,7 +5162,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="53">
         <v>51</v>
       </c>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="C53" s="62"/>
     </row>
-    <row r="54" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" ht="75" x14ac:dyDescent="0.25">
       <c r="A54" s="53">
         <v>51</v>
       </c>
@@ -5182,7 +5182,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="72" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" ht="75" x14ac:dyDescent="0.25">
       <c r="A55" s="53">
         <v>52</v>
       </c>
